--- a/output/topology_excel/12793.xlsx
+++ b/output/topology_excel/12793.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -520,18 +520,18 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -542,18 +542,18 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
         <v>13</v>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,18 +586,18 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,18 +608,18 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -630,18 +630,18 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,18 +652,18 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
@@ -682,24 +682,24 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>414</v>
+        <v>74</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>192</v>
+        <v>325</v>
       </c>
       <c r="F13" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>104</v>
+        <v>289</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,18 +762,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>440</v>
+        <v>152</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>302</v>
+        <v>114</v>
       </c>
       <c r="F16" t="n">
-        <v>213</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
@@ -795,7 +795,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>212</v>
+        <v>414</v>
       </c>
       <c r="F17" t="n">
-        <v>126</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -817,7 +817,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>199</v>
+        <v>440</v>
       </c>
       <c r="F20" t="n">
         <v>11</v>
@@ -880,7 +880,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B21" t="n">
         <v>8</v>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F21" t="n">
         <v>13</v>
@@ -905,7 +905,7 @@
         <v>5</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="F22" t="n">
         <v>13</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>405</v>
+        <v>181</v>
       </c>
       <c r="F23" t="n">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24">
@@ -949,29 +949,29 @@
         <v>6</v>
       </c>
       <c r="B24" t="n">
+        <v>14</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>87</v>
+      </c>
+      <c r="F24" t="n">
         <v>11</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>155</v>
-      </c>
-      <c r="F24" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,18 +1004,18 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>366</v>
+        <v>199</v>
       </c>
       <c r="F26" t="n">
-        <v>99</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>224</v>
+        <v>138</v>
       </c>
       <c r="F27" t="n">
-        <v>191</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,32 +1048,274 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>155</v>
+        <v>405</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>200</v>
+      </c>
+      <c r="F29" t="n">
         <v>12</v>
       </c>
-      <c r="B29" t="n">
-        <v>13</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>179</v>
+      </c>
+      <c r="F30" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>135</v>
+      </c>
+      <c r="F31" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" t="n">
+        <v>16</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>155</v>
+      </c>
+      <c r="F32" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" t="n">
+        <v>13</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>192</v>
+      </c>
+      <c r="F33" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" t="n">
+        <v>16</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>114</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>12</v>
+      </c>
+      <c r="B35" t="n">
+        <v>16</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
         <v>148</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F35" t="n">
         <v>33</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>13</v>
+      </c>
+      <c r="B36" t="n">
+        <v>14</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>185</v>
+      </c>
+      <c r="F36" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>14</v>
+      </c>
+      <c r="B37" t="n">
+        <v>15</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>161</v>
+      </c>
+      <c r="F37" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>289</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>175</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>6</v>
+      </c>
+      <c r="B40" t="n">
+        <v>14</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>157</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/12793.xlsx
+++ b/output/topology_excel/12793.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>11</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>11</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>13</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>11</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>13</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>13</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>12</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>13</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>51</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>13</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>13</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>13</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>13</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -759,12 +795,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>152</v>
+        <v>36</v>
       </c>
       <c r="F15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>105</v>
+      </c>
+      <c r="H15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -787,8 +829,10 @@
         <v>114</v>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +855,8 @@
       <c r="F17" t="n">
         <v>11</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -831,8 +877,10 @@
         <v>192</v>
       </c>
       <c r="F18" t="n">
-        <v>63</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +903,8 @@
       <c r="F19" t="n">
         <v>11</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +927,8 @@
       <c r="F20" t="n">
         <v>11</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +951,8 @@
       <c r="F21" t="n">
         <v>13</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +975,8 @@
       <c r="F22" t="n">
         <v>13</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -941,8 +997,10 @@
         <v>181</v>
       </c>
       <c r="F23" t="n">
-        <v>99</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1023,8 @@
       <c r="F24" t="n">
         <v>11</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -985,8 +1045,10 @@
         <v>180</v>
       </c>
       <c r="F25" t="n">
-        <v>77</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1071,8 @@
       <c r="F26" t="n">
         <v>11</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1095,8 @@
       <c r="F27" t="n">
         <v>13</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1051,8 +1117,10 @@
         <v>405</v>
       </c>
       <c r="F28" t="n">
-        <v>56</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1143,8 @@
       <c r="F29" t="n">
         <v>12</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1167,8 @@
       <c r="F30" t="n">
         <v>13</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1191,8 @@
       <c r="F31" t="n">
         <v>13</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1215,8 @@
       <c r="F32" t="n">
         <v>13</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1239,8 @@
       <c r="F33" t="n">
         <v>13</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1263,8 @@
       <c r="F34" t="n">
         <v>13</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1287,8 @@
       <c r="F35" t="n">
         <v>33</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1227,8 +1309,10 @@
         <v>185</v>
       </c>
       <c r="F36" t="n">
-        <v>99</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1249,8 +1333,10 @@
         <v>161</v>
       </c>
       <c r="F37" t="n">
-        <v>26</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1359,8 @@
       <c r="F38" t="n">
         <v>1</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1383,8 @@
       <c r="F39" t="n">
         <v>1</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1407,8 @@
       <c r="F40" t="n">
         <v>1</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
